--- a/data/trans_orig/P2A_fisi_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>29581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24406</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>46399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70010</t>
+          <t>69656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664406</t>
+          <t>664431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>682755</t>
+          <t>682105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641772</t>
+          <t>641952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663945</t>
+          <t>664448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1312353</t>
+          <t>1312707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1341264</t>
+          <t>1342052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39780</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69058</t>
+          <t>68437</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42354</t>
+          <t>42852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72031</t>
+          <t>74136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86986</t>
+          <t>88444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131247</t>
+          <t>128260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>892742</t>
+          <t>893363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>922020</t>
+          <t>922773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>896362</t>
+          <t>894257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>926039</t>
+          <t>925541</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1798946</t>
+          <t>1801933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1843207</t>
+          <t>1841749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52490</t>
+          <t>54369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29211</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54042</t>
+          <t>54650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63762</t>
+          <t>63162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98651</t>
+          <t>97419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626019</t>
+          <t>624140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>649341</t>
+          <t>650053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>629799</t>
+          <t>629191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654630</t>
+          <t>653937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1263699</t>
+          <t>1264931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298588</t>
+          <t>1299188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39893</t>
+          <t>38974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68213</t>
+          <t>67107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64041</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98345</t>
+          <t>98671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111805</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157008</t>
+          <t>156576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874009</t>
+          <t>875115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902329</t>
+          <t>903248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>940267</t>
+          <t>939941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>974571</t>
+          <t>975474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1823826</t>
+          <t>1824258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1869029</t>
+          <t>1868080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139518</t>
+          <t>140911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191126</t>
+          <t>188514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183046</t>
+          <t>185394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240842</t>
+          <t>242778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338131</t>
+          <t>341330</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>415727</t>
+          <t>414212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3085417</t>
+          <t>3088029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3137025</t>
+          <t>3135632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3138355</t>
+          <t>3136419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3196151</t>
+          <t>3193803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6240014</t>
+          <t>6241529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6317610</t>
+          <t>6314411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54324</t>
+          <t>54350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>42211</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72290</t>
+          <t>70909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79353</t>
+          <t>79011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116551</t>
+          <t>116995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649145</t>
+          <t>649119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>674859</t>
+          <t>675513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>624760</t>
+          <t>626141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>654826</t>
+          <t>654839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1283968</t>
+          <t>1283524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1321166</t>
+          <t>1321508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66258</t>
+          <t>65570</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102656</t>
+          <t>102786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84083</t>
+          <t>85666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124393</t>
+          <t>124037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>157999</t>
+          <t>159271</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214385</t>
+          <t>211393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>915291</t>
+          <t>915161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>951689</t>
+          <t>952377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>907791</t>
+          <t>908147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>948101</t>
+          <t>946518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1835746</t>
+          <t>1838738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1892132</t>
+          <t>1890860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42579</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>73640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49342</t>
+          <t>47694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83511</t>
+          <t>83723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100171</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146225</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>685191</t>
+          <t>683983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>715044</t>
+          <t>714993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693663</t>
+          <t>693451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>727832</t>
+          <t>729480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1388572</t>
+          <t>1389837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1434626</t>
+          <t>1434913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55519</t>
+          <t>53694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91358</t>
+          <t>91432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84324</t>
+          <t>82809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122175</t>
+          <t>122937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147153</t>
+          <t>149444</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200694</t>
+          <t>201345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856381</t>
+          <t>856307</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892220</t>
+          <t>894045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>929726</t>
+          <t>928964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>967577</t>
+          <t>969092</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1798946</t>
+          <t>1798295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1852487</t>
+          <t>1850196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>219117</t>
+          <t>222019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>283385</t>
+          <t>282813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287725</t>
+          <t>289062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>357100</t>
+          <t>360613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>527507</t>
+          <t>527858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>620899</t>
+          <t>621491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3143394</t>
+          <t>3143966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3207662</t>
+          <t>3204760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3201209</t>
+          <t>3197696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3270584</t>
+          <t>3269247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6364189</t>
+          <t>6363597</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6457581</t>
+          <t>6457230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34870</t>
+          <t>34777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61329</t>
+          <t>62218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>35494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61928</t>
+          <t>63748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77261</t>
+          <t>77178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117224</t>
+          <t>115113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>613471</t>
+          <t>612582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>639930</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>610911</t>
+          <t>609091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>637319</t>
+          <t>637345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1230415</t>
+          <t>1232526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1270378</t>
+          <t>1270461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39355</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67351</t>
+          <t>68429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57373</t>
+          <t>59533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94844</t>
+          <t>95627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104800</t>
+          <t>104847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149927</t>
+          <t>152251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>955080</t>
+          <t>954002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>983076</t>
+          <t>983824</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>948069</t>
+          <t>947286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>985540</t>
+          <t>983380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1915417</t>
+          <t>1913093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1960544</t>
+          <t>1960497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35378</t>
+          <t>35979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>54700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49334</t>
+          <t>49783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84425</t>
+          <t>85084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>724174</t>
+          <t>723573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>744082</t>
+          <t>744150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>731001</t>
+          <t>730311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>756629</t>
+          <t>756515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1460138</t>
+          <t>1459479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1495229</t>
+          <t>1494780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51963</t>
+          <t>51412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83929</t>
+          <t>81439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66422</t>
+          <t>64970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103214</t>
+          <t>102571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125337</t>
+          <t>124625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172638</t>
+          <t>176006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853638</t>
+          <t>856128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885604</t>
+          <t>886155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>940565</t>
+          <t>941208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>977357</t>
+          <t>978809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1808708</t>
+          <t>1805340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1856009</t>
+          <t>1856721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>161060</t>
+          <t>162097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>215899</t>
+          <t>216780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>214419</t>
+          <t>215180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>275554</t>
+          <t>277386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>392163</t>
+          <t>389233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>478357</t>
+          <t>476535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3178451</t>
+          <t>3177570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3233290</t>
+          <t>3232253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3268988</t>
+          <t>3267156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3330123</t>
+          <t>3329362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6460535</t>
+          <t>6462357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6546729</t>
+          <t>6549659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66268</t>
+          <t>66328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97901</t>
+          <t>98786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58289</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>90440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134105</t>
+          <t>134900</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182146</t>
+          <t>179694</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>537540</t>
+          <t>536655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>569173</t>
+          <t>569113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>635383</t>
+          <t>634890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667041</t>
+          <t>664523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1178626</t>
+          <t>1181078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1226667</t>
+          <t>1225872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64900</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155773</t>
+          <t>156152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112506</t>
+          <t>112291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146019</t>
+          <t>145544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>160225</t>
+          <t>161070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>286820</t>
+          <t>286541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1037091</t>
+          <t>1036712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1127964</t>
+          <t>1140666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>812632</t>
+          <t>813107</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>846145</t>
+          <t>846360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1864696</t>
+          <t>1864975</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1991291</t>
+          <t>1990446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70456</t>
+          <t>70780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111004</t>
+          <t>108565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98029</t>
+          <t>98240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>566033</t>
+          <t>603392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185443</t>
+          <t>186535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>784251</t>
+          <t>776728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>593676</t>
+          <t>596115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634224</t>
+          <t>633900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367333</t>
+          <t>329974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>835337</t>
+          <t>835126</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853795</t>
+          <t>861318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1452603</t>
+          <t>1451511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,61%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60947</t>
+          <t>61379</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92586</t>
+          <t>92070</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73429</t>
+          <t>73245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111401</t>
+          <t>111675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141439</t>
+          <t>141251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194242</t>
+          <t>193633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>834245</t>
+          <t>834761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>865884</t>
+          <t>865452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>983531</t>
+          <t>983257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1021503</t>
+          <t>1021687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1827521</t>
+          <t>1828130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1880324</t>
+          <t>1880512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>288845</t>
+          <t>280643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>406715</t>
+          <t>412039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>390677</t>
+          <t>390238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1159719</t>
+          <t>1157341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>739944</t>
+          <t>736831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1622589</t>
+          <t>1507037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3053102</t>
+          <t>3047778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3170972</t>
+          <t>3179174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2552561</t>
+          <t>2554939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3321603</t>
+          <t>3322042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5549508</t>
+          <t>5665060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6432153</t>
+          <t>6435266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_fisi_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29581</t>
+          <t>29315</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46399</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40311</t>
+          <t>41032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69656</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664431</t>
+          <t>664697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>682105</t>
+          <t>681947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641952</t>
+          <t>642643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664448</t>
+          <t>663138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1312707</t>
+          <t>1314818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1342052</t>
+          <t>1341331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39027</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68437</t>
+          <t>70053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42852</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74136</t>
+          <t>73397</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88444</t>
+          <t>87166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128260</t>
+          <t>130516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>893363</t>
+          <t>891747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>922773</t>
+          <t>922220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>894257</t>
+          <t>894996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>925541</t>
+          <t>926358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1801933</t>
+          <t>1799677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1841749</t>
+          <t>1843027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28456</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54369</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,44 +1439,44 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>40573</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>28935</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>54743</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>8,01%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>40573</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>29904</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>54650</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>77</t>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63162</t>
+          <t>63061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97419</t>
+          <t>98851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624140</t>
+          <t>625094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650053</t>
+          <t>650046</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,47 +1547,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>643268</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>629098</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>654906</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>91,99%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>643268</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>629191</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>653937</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1264931</t>
+          <t>1263499</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1299188</t>
+          <t>1299289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38974</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67107</t>
+          <t>67587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63138</t>
+          <t>65680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98671</t>
+          <t>100155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112754</t>
+          <t>110670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156576</t>
+          <t>154801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>875115</t>
+          <t>874635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>903248</t>
+          <t>903376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>939941</t>
+          <t>938457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>975474</t>
+          <t>972932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1824258</t>
+          <t>1826033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1868080</t>
+          <t>1870164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140911</t>
+          <t>138475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188514</t>
+          <t>189999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185394</t>
+          <t>182438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242778</t>
+          <t>241226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341330</t>
+          <t>338008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414212</t>
+          <t>411953</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3088029</t>
+          <t>3086544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3135632</t>
+          <t>3138068</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3136419</t>
+          <t>3137971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3193803</t>
+          <t>3196759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6241529</t>
+          <t>6243788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6314411</t>
+          <t>6317733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>54691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42211</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70909</t>
+          <t>71776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79011</t>
+          <t>77573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116995</t>
+          <t>115292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649119</t>
+          <t>648778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>675513</t>
+          <t>675403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>626141</t>
+          <t>625274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>654839</t>
+          <t>654489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1283524</t>
+          <t>1285227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1321508</t>
+          <t>1322946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65570</t>
+          <t>66232</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102786</t>
+          <t>102817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85666</t>
+          <t>85072</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124037</t>
+          <t>126247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159271</t>
+          <t>159570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211393</t>
+          <t>215212</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>915161</t>
+          <t>915130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>952377</t>
+          <t>951715</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>908147</t>
+          <t>905937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>946518</t>
+          <t>947112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1838738</t>
+          <t>1834919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1890860</t>
+          <t>1890561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>42693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73640</t>
+          <t>74713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47694</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83723</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99884</t>
+          <t>99713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>142376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>683983</t>
+          <t>682910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>714993</t>
+          <t>714930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693451</t>
+          <t>693994</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>729480</t>
+          <t>726596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1389837</t>
+          <t>1392421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1434913</t>
+          <t>1435084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53694</t>
+          <t>56345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>91499</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82809</t>
+          <t>81959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122937</t>
+          <t>121255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149444</t>
+          <t>146042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>201345</t>
+          <t>200232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856307</t>
+          <t>856240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>894045</t>
+          <t>891394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>928964</t>
+          <t>930646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>969092</t>
+          <t>969942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1798295</t>
+          <t>1799408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1850196</t>
+          <t>1853598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>222019</t>
+          <t>218116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>282813</t>
+          <t>285421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289062</t>
+          <t>287533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>360613</t>
+          <t>360504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>527858</t>
+          <t>527790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>621491</t>
+          <t>627280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3143966</t>
+          <t>3141358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3204760</t>
+          <t>3208663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3197696</t>
+          <t>3197805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3269247</t>
+          <t>3270776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6363597</t>
+          <t>6357808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6457230</t>
+          <t>6457298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34777</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62218</t>
+          <t>61365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35494</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63748</t>
+          <t>61833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77178</t>
+          <t>77297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115113</t>
+          <t>113911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>612582</t>
+          <t>613435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>640023</t>
+          <t>639641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>609091</t>
+          <t>611006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>637345</t>
+          <t>638366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1232526</t>
+          <t>1233728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1270461</t>
+          <t>1270342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>37856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68429</t>
+          <t>69409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59533</t>
+          <t>58883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95627</t>
+          <t>94903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104847</t>
+          <t>105835</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152251</t>
+          <t>151758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>954002</t>
+          <t>953022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>983824</t>
+          <t>984575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>947286</t>
+          <t>948010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>983380</t>
+          <t>984030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1913093</t>
+          <t>1913586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1960497</t>
+          <t>1959509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35979</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54700</t>
+          <t>55133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49783</t>
+          <t>49004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85084</t>
+          <t>83069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>723573</t>
+          <t>724250</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>744150</t>
+          <t>743734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>730311</t>
+          <t>729878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>756515</t>
+          <t>756502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1459479</t>
+          <t>1461494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1494780</t>
+          <t>1495559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51412</t>
+          <t>51416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81439</t>
+          <t>82503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64970</t>
+          <t>65513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102571</t>
+          <t>102030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124625</t>
+          <t>126243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176006</t>
+          <t>173320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856128</t>
+          <t>855064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886155</t>
+          <t>886151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>941208</t>
+          <t>941749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>978809</t>
+          <t>978266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1805340</t>
+          <t>1808026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1856721</t>
+          <t>1855103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>162097</t>
+          <t>163918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>216780</t>
+          <t>217219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>215180</t>
+          <t>213063</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>277386</t>
+          <t>274503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>389233</t>
+          <t>392156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>476535</t>
+          <t>470234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3177570</t>
+          <t>3177131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3232253</t>
+          <t>3230432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3267156</t>
+          <t>3270039</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3329362</t>
+          <t>3331479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6462357</t>
+          <t>6468658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6549659</t>
+          <t>6546736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>81254</t>
+          <t>85517</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66328</t>
+          <t>69536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98786</t>
+          <t>104370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>81007</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>69596</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90440</t>
+          <t>97235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>156956</t>
+          <t>166524</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134900</t>
+          <t>147182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>179694</t>
+          <t>189953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>554187</t>
+          <t>605193</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>536655</t>
+          <t>586340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>569113</t>
+          <t>621174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>649628</t>
+          <t>653173</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634890</t>
+          <t>636945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664523</t>
+          <t>664584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1203816</t>
+          <t>1258365</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1181078</t>
+          <t>1234936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1225872</t>
+          <t>1277707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>116030</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>102691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156152</t>
+          <t>149453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>128812</t>
+          <t>143077</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112291</t>
+          <t>125575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145544</t>
+          <t>162048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>244842</t>
+          <t>267335</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161070</t>
+          <t>240686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>286541</t>
+          <t>299142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1076834</t>
+          <t>924659</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1036712</t>
+          <t>899464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1140666</t>
+          <t>946226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>829839</t>
+          <t>928397</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>813107</t>
+          <t>909426</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>846360</t>
+          <t>945899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1906674</t>
+          <t>1853056</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1864975</t>
+          <t>1821249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1990446</t>
+          <t>1879705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88974</t>
+          <t>96243</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70780</t>
+          <t>77590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108565</t>
+          <t>117136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>286809</t>
+          <t>99751</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98240</t>
+          <t>83533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>603392</t>
+          <t>116436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>375783</t>
+          <t>195994</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186535</t>
+          <t>172983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>776728</t>
+          <t>221345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>615706</t>
+          <t>706830</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596115</t>
+          <t>685937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633900</t>
+          <t>725483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>646557</t>
+          <t>712508</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329974</t>
+          <t>695823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>835126</t>
+          <t>728726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1262263</t>
+          <t>1419338</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>861318</t>
+          <t>1393987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1451511</t>
+          <t>1442349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75733</t>
+          <t>77657</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61379</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92070</t>
+          <t>94666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92787</t>
+          <t>103580</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73245</t>
+          <t>88048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111675</t>
+          <t>121331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>168520</t>
+          <t>181237</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141251</t>
+          <t>161040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193633</t>
+          <t>206920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>851098</t>
+          <t>912405</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>834761</t>
+          <t>895396</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>865452</t>
+          <t>926317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1002145</t>
+          <t>1015461</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>983257</t>
+          <t>997710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1021687</t>
+          <t>1030993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1853243</t>
+          <t>1927867</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1828130</t>
+          <t>1902184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1880512</t>
+          <t>1948064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>361991</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>280643</t>
+          <t>346484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>412039</t>
+          <t>422103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>584109</t>
+          <t>427416</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>390238</t>
+          <t>398113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1157341</t>
+          <t>463994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>946100</t>
+          <t>811091</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>736831</t>
+          <t>764914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1507037</t>
+          <t>862677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3097826</t>
+          <t>3149086</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3047778</t>
+          <t>3110659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3179174</t>
+          <t>3186278</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3128171</t>
+          <t>3309538</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2554939</t>
+          <t>3272960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3322042</t>
+          <t>3338841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6225997</t>
+          <t>6458625</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5665060</t>
+          <t>6407039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6435266</t>
+          <t>6504802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_fisi_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
